--- a/backups/lcsc_inventory_backup_20261024_1104.xlsx
+++ b/backups/lcsc_inventory_backup_20261024_1104.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="469">
   <si>
     <t>项目</t>
   </si>
@@ -34,7 +34,7 @@
     <t>导出时间</t>
   </si>
   <si>
-    <t>2026-10-24 11:04:19</t>
+    <t>2026-10-24 11:04:58</t>
   </si>
   <si>
     <t>schema</t>
@@ -136,936 +136,969 @@
     <t>0603</t>
   </si>
   <si>
+    <t>2026-10-24 11:04:28</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:04:39</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:38:17</t>
+  </si>
+  <si>
+    <t>电容</t>
+  </si>
+  <si>
+    <t>贴片电容(MLCC)</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:44:18</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:12:02</t>
+  </si>
+  <si>
+    <t>电阻</t>
+  </si>
+  <si>
+    <t>电流采样电阻/分流器</t>
+  </si>
+  <si>
+    <t>2026-10-24 11:01:01</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:47:52</t>
+  </si>
+  <si>
+    <t>料号</t>
+  </si>
+  <si>
+    <t>厂牌料号</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>品牌</t>
+  </si>
+  <si>
+    <t>封装</t>
+  </si>
+  <si>
+    <t>类目</t>
+  </si>
+  <si>
+    <t>规格</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>商品链接</t>
+  </si>
+  <si>
+    <t>规格书链接</t>
+  </si>
+  <si>
+    <t>单价</t>
+  </si>
+  <si>
+    <t>低库存阈值</t>
+  </si>
+  <si>
+    <t>具体位置</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>预览图</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>0欧</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>{"阻值":"0r","精度":"5%"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 A1</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:46:34</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>8.45k</t>
+  </si>
+  <si>
+    <t>{"阻值":"8.45k","精度":"±1%"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 B1</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:51:27</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>28k</t>
+  </si>
+  <si>
+    <t>{"精度":"±1%"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 C1</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:52:58</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>150R</t>
+  </si>
+  <si>
+    <t>磁珠</t>
+  </si>
+  <si>
+    <t>{"精度":"±25% 2a"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 D1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:02:00</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>10uf</t>
+  </si>
+  <si>
+    <t>{"耐压":"6.3v"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 A5</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:55:42</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>{"耐压":"x5r ±10% 10v"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 B5</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:58:46</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>{"耐压":"X7R ±10%"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 C5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:00:07</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>100nf</t>
+  </si>
+  <si>
+    <t>{"耐压":"±10% 50v"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 D5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:00:48</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>47pf</t>
+  </si>
+  <si>
+    <t>{"耐压":"±5%"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 E5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:03:09</t>
+  </si>
+  <si>
+    <t>C338080</t>
+  </si>
+  <si>
+    <t>C2012X5R1V226MT000E</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>0805</t>
+  </si>
+  <si>
+    <t>{"容值":"22uF","精度":"±20%","额定电压":"35V","温度系数":"X5R"}</t>
+  </si>
+  <si>
+    <t>C2012X5R1V226M125AC</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/315873.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20190306/C361202_7784D5A6541933BE8E83CE426B620009.pdf</t>
+  </si>
+  <si>
+    <t>1.9017</t>
+  </si>
+  <si>
+    <t>阻容盒子 G5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:17:29</t>
+  </si>
+  <si>
+    <t>C77055</t>
+  </si>
+  <si>
+    <t>GRM188R71H104KA93D</t>
+  </si>
+  <si>
+    <t>muRata(村田)</t>
+  </si>
+  <si>
+    <t>{"容值":"100nF","精度":"±10%","额定电压":"50V","温度系数":"X7R"}</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/78182.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20200305/C490387_23319AE8C154DEB24C505E6C82A8106A.pdf</t>
+  </si>
+  <si>
+    <t>0.0742</t>
+  </si>
+  <si>
+    <t>阻容盒子 H5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:17:07</t>
+  </si>
+  <si>
+    <t>C010</t>
+  </si>
+  <si>
+    <t>{"耐压":"16v"}</t>
+  </si>
+  <si>
+    <t>阻容盒子 F5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:19:35</t>
+  </si>
+  <si>
+    <t>C162273</t>
+  </si>
+  <si>
+    <t>GRM188R61H225KE11D</t>
+  </si>
+  <si>
+    <t>{"容值":"2.2uF","精度":"±10%","额定电压":"50V","温度系数":"X5R"}</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/173654.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20181211/C162273_A9C6FF7829784AEF50225F4680DD9126.pdf</t>
+  </si>
+  <si>
+    <t>0.2815</t>
+  </si>
+  <si>
+    <t>阻容盒子 I5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:20:56</t>
+  </si>
+  <si>
+    <t>C77082</t>
+  </si>
+  <si>
+    <t>GRM21BR71H104KA01L</t>
+  </si>
+  <si>
+    <t>材质:X7R</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/78209.html</t>
+  </si>
+  <si>
+    <t>0.1782</t>
+  </si>
+  <si>
+    <t>阻容盒子 J5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:23:10</t>
+  </si>
+  <si>
+    <t>C7467115</t>
+  </si>
+  <si>
+    <t>FCC0603N331J500CT</t>
+  </si>
+  <si>
+    <t>FOJAN(富捷)</t>
+  </si>
+  <si>
+    <t>{"容值":"330pF","精度":"±5%","额定电压":"50V","温度系数":"C0G"}</t>
+  </si>
+  <si>
+    <t>COG类介质材料的电容器为I类电容器,包括常规、中高压COG产品。此类产品电性能稳定,几乎不随温度、电压和时间的变化而变化,适用于低损耗,稳定性要求高的电路中,如滤波器、谐振器和计时电路中。X7R、X5R、X6S、X7T类介质材料的电容器为II类电容器,具有较高的介电常数,容量比I类电容器高,具有较稳定的温度特性,适用于容量范围广,稳定性要求不高的电路中,如隔直、耦合、旁路、鉴频等电路中。Y5V类介质材料的电容器为II类电容器,是所有电容器中介电常数最大的电容器,但其容量稳定性较差,对温度、电压等条件较敏感,适用于要求大容量,温度变化不大的电路中。</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/8513652.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260824/C7059AD86670CB03FD643668122C4D10.pdf</t>
+  </si>
+  <si>
+    <t>0.0465</t>
+  </si>
+  <si>
+    <t>阻容盒子 K5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:24:56</t>
+  </si>
+  <si>
+    <t>C6119901</t>
+  </si>
+  <si>
+    <t>CGA0805X5R226M350MT</t>
+  </si>
+  <si>
+    <t>HRE(芯声)</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/7062607.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260507/1E5DA6BD55BD882EF53B40E61E6E4459.pdf</t>
+  </si>
+  <si>
+    <t>1.0744</t>
+  </si>
+  <si>
+    <t>阻容盒子 L5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:26:58</t>
+  </si>
+  <si>
+    <t>C5137636</t>
+  </si>
+  <si>
+    <t>FCC0603B104K500CT</t>
+  </si>
+  <si>
+    <t>COG 此类介质材料的电容器为 I 类电容器,电性能稳定,几乎不随温度、电压和时间的变化而变化,适用于低损耗,稳定性要求高的电路。X7R、X5R、X6S、X7T 此类介质材料的电容器为II类电容器,具有较高的介电常数,容量比 I 类电容器高,具有较稳定的温度特性,适用于容量范围广,稳定性要求不高的电路。Y5V 此类介质材料的电容器为II类电容器,是所有电容器中介电常数最大的电容器,但其容量稳定性较差,对温度、电压等条件较敏感,适用于要求大容量,温度变化不大的电路。</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/5747088.html</t>
+  </si>
+  <si>
+    <t>0.0388</t>
+  </si>
+  <si>
+    <t>阻容盒子 M5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:28:30</t>
+  </si>
+  <si>
+    <t>C1664</t>
+  </si>
+  <si>
+    <t>CL10C331JB8NNNC</t>
+  </si>
+  <si>
+    <t>SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/2016.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</t>
+  </si>
+  <si>
+    <t>0.1099</t>
+  </si>
+  <si>
+    <t>阻容盒子 N5</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:31:01</t>
+  </si>
+  <si>
+    <t>C52037858</t>
+  </si>
+  <si>
+    <t>CSA0603X5R106M160JT</t>
+  </si>
+  <si>
+    <t>{"容值":"10uF","精度":"±20%","额定电压":"16V","温度系数":"X5R"}</t>
+  </si>
+  <si>
+    <t>容值：10uF 精度：±20% 额定电压：16V 材质(温度系数)：X5R 材质：X5R</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/54798746.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20251009/B54053B702033BC9462E447A0A6C1DB6.pdf</t>
+  </si>
+  <si>
+    <t>0.166</t>
+  </si>
+  <si>
+    <t>阻容盒子 O5</t>
+  </si>
+  <si>
+    <t>C2906983</t>
+  </si>
+  <si>
+    <t>FRC0603F10R0TS</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"厚膜电阻","阻值":"10Ω","精度":"±1%","功率":"100mW"}</t>
+  </si>
+  <si>
+    <t>通用型， 工业级标准，ROHS</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/3180496.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260709/B4EE044C0739CE7C55D989F6D04C0F9E.pdf</t>
+  </si>
+  <si>
+    <t>0.0113</t>
+  </si>
+  <si>
+    <t>阻容盒子 E1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:46:30</t>
+  </si>
+  <si>
+    <t>C2906993</t>
+  </si>
+  <si>
+    <t>FRC0603F1503TS</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"厚膜电阻","阻值":"150kΩ","精度":"±1%","功率":"100mW"}</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/3180506.html</t>
+  </si>
+  <si>
+    <t>0.0124</t>
+  </si>
+  <si>
+    <t>阻容盒子 F1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:48:44</t>
+  </si>
+  <si>
+    <t>C2907005</t>
+  </si>
+  <si>
+    <t>FRC0603F2201TS</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"厚膜电阻","阻值":"2.2kΩ","精度":"±1%","功率":"100mW"}</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/3180518.html</t>
+  </si>
+  <si>
+    <t>0.0114</t>
+  </si>
+  <si>
+    <t>阻容盒子 G1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:49:51</t>
+  </si>
+  <si>
+    <t>C23186</t>
+  </si>
+  <si>
+    <t>0603WAF5101T5E</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"厚膜电阻","阻值":"5.1kΩ","精度":"±1%","功率":"100mW"}</t>
+  </si>
+  <si>
+    <t>小尺寸、重量轻。降低组装成本,与贴片机匹配。适用于波峰焊和回流焊</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/23913.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20200306/C422600_1E6D84923E4A46A82E41ADD87F860B5C.pdf</t>
+  </si>
+  <si>
+    <t>0.0091</t>
+  </si>
+  <si>
+    <t>阻容盒子 H1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:51:07</t>
+  </si>
+  <si>
+    <t>C49196669</t>
+  </si>
+  <si>
+    <t>FRH0603B2002TS</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"厚膜电阻","阻值":"20kΩ","精度":"±0.1%","功率":"100mW"}</t>
+  </si>
+  <si>
+    <t>高精度，厚膜贴片电阻；工业级标准，ROHS</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/51598967.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260115/3F2191DDE93B91B57387A2F2C8E8604C.pdf</t>
+  </si>
+  <si>
+    <t>0.0533</t>
+  </si>
+  <si>
+    <t>阻容盒子 I1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:52:32</t>
+  </si>
+  <si>
+    <t>C316397</t>
+  </si>
+  <si>
+    <t>SDNT1608X103F3380FTF</t>
+  </si>
+  <si>
+    <t>Sunlord(顺络)</t>
+  </si>
+  <si>
+    <t>NTC热敏电阻</t>
+  </si>
+  <si>
+    <t>{"功率":"100mW","阻值":"10kΩ","电阻精度":"±1%","B值精度":"±1%"}</t>
+  </si>
+  <si>
+    <t>特性：SMD结构适合高密度安装。 B值种类多可满足各种应用。 良好的焊接性能。应用：移动电话、智能手表、TWS耳机等便携式产品。 打印机、传真机、文字处理机等办公设备</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/298016.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20250613/843D00CF2C300AE0276A3364ED88CCAD.pdf</t>
+  </si>
+  <si>
+    <t>0.1321</t>
+  </si>
+  <si>
+    <t>阻容盒子 J1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:56:21</t>
+  </si>
+  <si>
+    <t>C2907048</t>
+  </si>
+  <si>
+    <t>FRC0603F5100TS</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"厚膜电阻","阻值":"510Ω","精度":"±1%","功率":"100mW"}</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/3180561.html</t>
+  </si>
+  <si>
+    <t>0.0135</t>
+  </si>
+  <si>
+    <t>阻容盒子 K1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:57:28</t>
+  </si>
+  <si>
+    <t>C2930027</t>
+  </si>
+  <si>
+    <t>FRC0603J103 TS</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"厚膜电阻","阻值":"10kΩ","精度":"±5%","功率":"100mW"}</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/3266960.html</t>
+  </si>
+  <si>
+    <t>0.0103</t>
+  </si>
+  <si>
+    <t>阻容盒子 L1</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:58:53</t>
+  </si>
+  <si>
+    <t>C7467248</t>
+  </si>
+  <si>
+    <t>FRM121WFR010TM</t>
+  </si>
+  <si>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"采样电阻","阻值":"10mΩ","精度":"±1%","功率":"1W"}</t>
+  </si>
+  <si>
+    <t>合金电阻，金属电阻，取样电阻，分流检测电阻，低温漂；</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/8513848.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260709/DBB5446AC05B7E4BE86547E1063AF3FD.pdf</t>
+  </si>
+  <si>
+    <t>0.2153</t>
+  </si>
+  <si>
+    <t>阻容盒子 M1</t>
+  </si>
+  <si>
+    <t>2026-10-24 11:02:55</t>
+  </si>
+  <si>
+    <t>C49164933</t>
+  </si>
+  <si>
+    <t>JER1206F1R003</t>
+  </si>
+  <si>
+    <t>JIERR(捷而瑞)</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"采样电阻","阻值":"3mΩ","精度":"±1%","功率":"1W"}</t>
+  </si>
+  <si>
+    <t>用于电流检测,SMD贴片安装,高功率,超低阻值(低至0.0R)</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/51553068.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20250822/103F28B376D35713A4298AA1547AE93B.pdf</t>
+  </si>
+  <si>
+    <t>0.3175</t>
+  </si>
+  <si>
+    <t>阻容盒子 N1</t>
+  </si>
+  <si>
+    <t>2026-10-24 11:03:49</t>
+  </si>
+  <si>
+    <t>C2988648</t>
+  </si>
+  <si>
+    <t>HoLLR1206-1W-5mR-1%</t>
+  </si>
+  <si>
+    <t>Milliohm(毫欧)</t>
+  </si>
+  <si>
+    <t>{"电阻类型":"采样电阻","阻值":"5mΩ","精度":"±1%","功率":"1W"}</t>
+  </si>
+  <si>
+    <t>特性：厚实的铜材质导体。金属化的材质。超长期的稳定性。无卤素无铅,符合RoHS。稳定的材料。高额定功率。应用：电池管理系统(BMS)。电流感测与分压</t>
+  </si>
+  <si>
+    <t>https://item.szlcsc.com/3447055.html</t>
+  </si>
+  <si>
+    <t>https://atta.szlcsc.com/upload/public/pdf/source/20220407/F189C92CC2C10DCB4BF36375122B9E11.pdf</t>
+  </si>
+  <si>
+    <t>0.3365</t>
+  </si>
+  <si>
+    <t>阻容盒子 O1</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>行数</t>
+  </si>
+  <si>
+    <t>列数</t>
+  </si>
+  <si>
+    <t>入库库位</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>阻容盒子</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:08:52</t>
+  </si>
+  <si>
+    <t>容器id</t>
+  </si>
+  <si>
+    <t>行</t>
+  </si>
+  <si>
+    <t>列</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>库位编号</t>
+  </si>
+  <si>
+    <t>最近入库时间</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:11:20</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:54:24</t>
+  </si>
+  <si>
+    <t>2026-10-24 09:57:01</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:08:13</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:20:28</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:22:57</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:24:08</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:25:58</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:28:04</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:29:05</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:55:58</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>2026-10-24 10:58:52</t>
+  </si>
+  <si>
     <t>2026-10-24 11:00:16</t>
   </si>
   <si>
-    <t>2026-10-24 09:04:39</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:38:17</t>
-  </si>
-  <si>
-    <t>电容</t>
-  </si>
-  <si>
-    <t>贴片电容(MLCC)</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:44:18</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:12:02</t>
-  </si>
-  <si>
-    <t>电阻</t>
-  </si>
-  <si>
-    <t>电流采样电阻/分流器</t>
-  </si>
-  <si>
-    <t>2026-10-24 11:01:01</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:47:52</t>
-  </si>
-  <si>
-    <t>料号</t>
-  </si>
-  <si>
-    <t>厂牌料号</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>品牌</t>
-  </si>
-  <si>
-    <t>封装</t>
-  </si>
-  <si>
-    <t>类目</t>
-  </si>
-  <si>
-    <t>规格</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>商品链接</t>
-  </si>
-  <si>
-    <t>规格书链接</t>
-  </si>
-  <si>
-    <t>单价</t>
-  </si>
-  <si>
-    <t>低库存阈值</t>
-  </si>
-  <si>
-    <t>具体位置</t>
-  </si>
-  <si>
-    <t>更新时间</t>
-  </si>
-  <si>
-    <t>预览图</t>
-  </si>
-  <si>
-    <t>C01</t>
-  </si>
-  <si>
-    <t>0欧</t>
-  </si>
-  <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>{"阻值":"0r","精度":"5%"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 A1</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:46:34</t>
-  </si>
-  <si>
-    <t>C02</t>
-  </si>
-  <si>
-    <t>8.45k</t>
-  </si>
-  <si>
-    <t>{"阻值":"8.45k","精度":"±1%"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 B1</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:51:27</t>
-  </si>
-  <si>
-    <t>C03</t>
-  </si>
-  <si>
-    <t>28k</t>
-  </si>
-  <si>
-    <t>{"精度":"±1%"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 C1</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:52:58</t>
-  </si>
-  <si>
-    <t>C04</t>
-  </si>
-  <si>
-    <t>150R</t>
-  </si>
-  <si>
-    <t>磁珠</t>
-  </si>
-  <si>
-    <t>{"精度":"±25% 2a"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 D1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:02:00</t>
-  </si>
-  <si>
-    <t>C05</t>
-  </si>
-  <si>
-    <t>10uf</t>
-  </si>
-  <si>
-    <t>{"耐压":"6.3v"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 A5</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:55:42</t>
-  </si>
-  <si>
-    <t>C06</t>
-  </si>
-  <si>
-    <t>{"耐压":"x5r ±10% 10v"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 B5</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:58:46</t>
-  </si>
-  <si>
-    <t>C07</t>
-  </si>
-  <si>
-    <t>{"耐压":"X7R ±10%"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 C5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:00:07</t>
-  </si>
-  <si>
-    <t>C08</t>
-  </si>
-  <si>
-    <t>100nf</t>
-  </si>
-  <si>
-    <t>{"耐压":"±10% 50v"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 D5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:00:48</t>
-  </si>
-  <si>
-    <t>C09</t>
-  </si>
-  <si>
-    <t>47pf</t>
-  </si>
-  <si>
-    <t>{"耐压":"±5%"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 E5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:03:09</t>
-  </si>
-  <si>
-    <t>C338080</t>
-  </si>
-  <si>
-    <t>C2012X5R1V226MT000E</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>0805</t>
-  </si>
-  <si>
-    <t>{"容值":"22uF","精度":"±20%","额定电压":"35V","温度系数":"X5R"}</t>
-  </si>
-  <si>
-    <t>C2012X5R1V226M125AC</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/315873.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20190306/C361202_7784D5A6541933BE8E83CE426B620009.pdf</t>
-  </si>
-  <si>
-    <t>1.9017</t>
-  </si>
-  <si>
-    <t>阻容盒子 G5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:17:29</t>
-  </si>
-  <si>
-    <t>C77055</t>
-  </si>
-  <si>
-    <t>GRM188R71H104KA93D</t>
-  </si>
-  <si>
-    <t>muRata(村田)</t>
-  </si>
-  <si>
-    <t>{"容值":"100nF","精度":"±10%","额定电压":"50V","温度系数":"X7R"}</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/78182.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20200305/C490387_23319AE8C154DEB24C505E6C82A8106A.pdf</t>
-  </si>
-  <si>
-    <t>0.0742</t>
-  </si>
-  <si>
-    <t>阻容盒子 H5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:17:07</t>
-  </si>
-  <si>
-    <t>C010</t>
-  </si>
-  <si>
-    <t>{"耐压":"16v"}</t>
-  </si>
-  <si>
-    <t>阻容盒子 F5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:19:35</t>
-  </si>
-  <si>
-    <t>C162273</t>
-  </si>
-  <si>
-    <t>GRM188R61H225KE11D</t>
-  </si>
-  <si>
-    <t>{"容值":"2.2uF","精度":"±10%","额定电压":"50V","温度系数":"X5R"}</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/173654.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20181211/C162273_A9C6FF7829784AEF50225F4680DD9126.pdf</t>
-  </si>
-  <si>
-    <t>0.2815</t>
-  </si>
-  <si>
-    <t>阻容盒子 I5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:20:56</t>
-  </si>
-  <si>
-    <t>C77082</t>
-  </si>
-  <si>
-    <t>GRM21BR71H104KA01L</t>
-  </si>
-  <si>
-    <t>材质:X7R</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/78209.html</t>
-  </si>
-  <si>
-    <t>0.1782</t>
-  </si>
-  <si>
-    <t>阻容盒子 J5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:23:10</t>
-  </si>
-  <si>
-    <t>C7467115</t>
-  </si>
-  <si>
-    <t>FCC0603N331J500CT</t>
-  </si>
-  <si>
-    <t>FOJAN(富捷)</t>
-  </si>
-  <si>
-    <t>{"容值":"330pF","精度":"±5%","额定电压":"50V","温度系数":"C0G"}</t>
-  </si>
-  <si>
-    <t>COG类介质材料的电容器为I类电容器,包括常规、中高压COG产品。此类产品电性能稳定,几乎不随温度、电压和时间的变化而变化,适用于低损耗,稳定性要求高的电路中,如滤波器、谐振器和计时电路中。X7R、X5R、X6S、X7T类介质材料的电容器为II类电容器,具有较高的介电常数,容量比I类电容器高,具有较稳定的温度特性,适用于容量范围广,稳定性要求不高的电路中,如隔直、耦合、旁路、鉴频等电路中。Y5V类介质材料的电容器为II类电容器,是所有电容器中介电常数最大的电容器,但其容量稳定性较差,对温度、电压等条件较敏感,适用于要求大容量,温度变化不大的电路中。</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/8513652.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260824/C7059AD86670CB03FD643668122C4D10.pdf</t>
-  </si>
-  <si>
-    <t>0.0465</t>
-  </si>
-  <si>
-    <t>阻容盒子 K5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:24:56</t>
-  </si>
-  <si>
-    <t>C6119901</t>
-  </si>
-  <si>
-    <t>CGA0805X5R226M350MT</t>
-  </si>
-  <si>
-    <t>HRE(芯声)</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/7062607.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260507/1E5DA6BD55BD882EF53B40E61E6E4459.pdf</t>
-  </si>
-  <si>
-    <t>1.0744</t>
-  </si>
-  <si>
-    <t>阻容盒子 L5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:26:58</t>
-  </si>
-  <si>
-    <t>C5137636</t>
-  </si>
-  <si>
-    <t>FCC0603B104K500CT</t>
-  </si>
-  <si>
-    <t>COG 此类介质材料的电容器为 I 类电容器,电性能稳定,几乎不随温度、电压和时间的变化而变化,适用于低损耗,稳定性要求高的电路。X7R、X5R、X6S、X7T 此类介质材料的电容器为II类电容器,具有较高的介电常数,容量比 I 类电容器高,具有较稳定的温度特性,适用于容量范围广,稳定性要求不高的电路。Y5V 此类介质材料的电容器为II类电容器,是所有电容器中介电常数最大的电容器,但其容量稳定性较差,对温度、电压等条件较敏感,适用于要求大容量,温度变化不大的电路。</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/5747088.html</t>
-  </si>
-  <si>
-    <t>0.0388</t>
-  </si>
-  <si>
-    <t>阻容盒子 M5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:28:30</t>
-  </si>
-  <si>
-    <t>C1664</t>
-  </si>
-  <si>
-    <t>CL10C331JB8NNNC</t>
-  </si>
-  <si>
-    <t>SAMSUNG(三星)</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/2016.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</t>
-  </si>
-  <si>
-    <t>0.1099</t>
-  </si>
-  <si>
-    <t>阻容盒子 N5</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:31:01</t>
-  </si>
-  <si>
-    <t>C52037858</t>
-  </si>
-  <si>
-    <t>CSA0603X5R106M160JT</t>
-  </si>
-  <si>
-    <t>{"容值":"10uF","精度":"±20%","额定电压":"16V","温度系数":"X5R"}</t>
-  </si>
-  <si>
-    <t>容值：10uF 精度：±20% 额定电压：16V 材质(温度系数)：X5R 材质：X5R</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/54798746.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20251009/B54053B702033BC9462E447A0A6C1DB6.pdf</t>
-  </si>
-  <si>
-    <t>0.166</t>
-  </si>
-  <si>
-    <t>阻容盒子 O5</t>
-  </si>
-  <si>
-    <t>C2906983</t>
-  </si>
-  <si>
-    <t>FRC0603F10R0TS</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"厚膜电阻","阻值":"10Ω","精度":"±1%","功率":"100mW"}</t>
-  </si>
-  <si>
-    <t>通用型， 工业级标准，ROHS</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/3180496.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260709/B4EE044C0739CE7C55D989F6D04C0F9E.pdf</t>
-  </si>
-  <si>
-    <t>0.0113</t>
-  </si>
-  <si>
-    <t>阻容盒子 E1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:46:30</t>
-  </si>
-  <si>
-    <t>C2906993</t>
-  </si>
-  <si>
-    <t>FRC0603F1503TS</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"厚膜电阻","阻值":"150kΩ","精度":"±1%","功率":"100mW"}</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/3180506.html</t>
-  </si>
-  <si>
-    <t>0.0124</t>
-  </si>
-  <si>
-    <t>阻容盒子 F1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:48:44</t>
-  </si>
-  <si>
-    <t>C2907005</t>
-  </si>
-  <si>
-    <t>FRC0603F2201TS</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"厚膜电阻","阻值":"2.2kΩ","精度":"±1%","功率":"100mW"}</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/3180518.html</t>
-  </si>
-  <si>
-    <t>0.0114</t>
-  </si>
-  <si>
-    <t>阻容盒子 G1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:49:51</t>
-  </si>
-  <si>
-    <t>C23186</t>
-  </si>
-  <si>
-    <t>0603WAF5101T5E</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"厚膜电阻","阻值":"5.1kΩ","精度":"±1%","功率":"100mW"}</t>
-  </si>
-  <si>
-    <t>小尺寸、重量轻。降低组装成本,与贴片机匹配。适用于波峰焊和回流焊</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/23913.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20200306/C422600_1E6D84923E4A46A82E41ADD87F860B5C.pdf</t>
-  </si>
-  <si>
-    <t>0.0091</t>
-  </si>
-  <si>
-    <t>阻容盒子 H1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:51:07</t>
-  </si>
-  <si>
-    <t>C49196669</t>
-  </si>
-  <si>
-    <t>FRH0603B2002TS</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"厚膜电阻","阻值":"20kΩ","精度":"±0.1%","功率":"100mW"}</t>
-  </si>
-  <si>
-    <t>高精度，厚膜贴片电阻；工业级标准，ROHS</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/51598967.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260115/3F2191DDE93B91B57387A2F2C8E8604C.pdf</t>
-  </si>
-  <si>
-    <t>0.0533</t>
-  </si>
-  <si>
-    <t>阻容盒子 I1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:52:32</t>
-  </si>
-  <si>
-    <t>C316397</t>
-  </si>
-  <si>
-    <t>SDNT1608X103F3380FTF</t>
-  </si>
-  <si>
-    <t>Sunlord(顺络)</t>
-  </si>
-  <si>
-    <t>NTC热敏电阻</t>
-  </si>
-  <si>
-    <t>{"功率":"100mW","阻值":"10kΩ","电阻精度":"±1%","B值精度":"±1%"}</t>
-  </si>
-  <si>
-    <t>特性：SMD结构适合高密度安装。 B值种类多可满足各种应用。 良好的焊接性能。应用：移动电话、智能手表、TWS耳机等便携式产品。 打印机、传真机、文字处理机等办公设备</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/298016.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20250613/843D00CF2C300AE0276A3364ED88CCAD.pdf</t>
-  </si>
-  <si>
-    <t>0.1321</t>
-  </si>
-  <si>
-    <t>阻容盒子 J1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:56:21</t>
-  </si>
-  <si>
-    <t>C2907048</t>
-  </si>
-  <si>
-    <t>FRC0603F5100TS</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"厚膜电阻","阻值":"510Ω","精度":"±1%","功率":"100mW"}</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/3180561.html</t>
-  </si>
-  <si>
-    <t>0.0135</t>
-  </si>
-  <si>
-    <t>阻容盒子 K1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:57:28</t>
-  </si>
-  <si>
-    <t>C2930027</t>
-  </si>
-  <si>
-    <t>FRC0603J103 TS</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"厚膜电阻","阻值":"10kΩ","精度":"±5%","功率":"100mW"}</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/3266960.html</t>
-  </si>
-  <si>
-    <t>0.0103</t>
-  </si>
-  <si>
-    <t>阻容盒子 L1</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:58:53</t>
-  </si>
-  <si>
-    <t>C7467248</t>
-  </si>
-  <si>
-    <t>FRM121WFR010TM</t>
-  </si>
-  <si>
-    <t>1206</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"采样电阻","阻值":"10mΩ","精度":"±1%","功率":"1W"}</t>
-  </si>
-  <si>
-    <t>合金电阻，金属电阻，取样电阻，分流检测电阻，低温漂；</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/8513848.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20260709/DBB5446AC05B7E4BE86547E1063AF3FD.pdf</t>
-  </si>
-  <si>
-    <t>0.2153</t>
-  </si>
-  <si>
-    <t>阻容盒子 M1</t>
-  </si>
-  <si>
-    <t>2026-10-24 11:02:55</t>
-  </si>
-  <si>
-    <t>C49164933</t>
-  </si>
-  <si>
-    <t>JER1206F1R003</t>
-  </si>
-  <si>
-    <t>JIERR(捷而瑞)</t>
-  </si>
-  <si>
-    <t>{"电阻类型":"采样电阻","阻值":"3mΩ","精度":"±1%","功率":"1W"}</t>
-  </si>
-  <si>
-    <t>用于电流检测,SMD贴片安装,高功率,超低阻值(低至0.0R)</t>
-  </si>
-  <si>
-    <t>https://item.szlcsc.com/51553068.html</t>
-  </si>
-  <si>
-    <t>https://atta.szlcsc.com/upload/public/pdf/source/20250822/103F28B376D35713A4298AA1547AE93B.pdf</t>
-  </si>
-  <si>
-    <t>0.3175</t>
-  </si>
-  <si>
-    <t>阻容盒子 N1</t>
-  </si>
-  <si>
-    <t>2026-10-24 11:03:49</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>行数</t>
-  </si>
-  <si>
-    <t>列数</t>
-  </si>
-  <si>
-    <t>入库库位</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>阻容盒子</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:08:52</t>
-  </si>
-  <si>
-    <t>容器id</t>
-  </si>
-  <si>
-    <t>行</t>
-  </si>
-  <si>
-    <t>列</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>库位编号</t>
-  </si>
-  <si>
-    <t>最近入库时间</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:11:20</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:54:24</t>
-  </si>
-  <si>
-    <t>2026-10-24 09:57:01</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:08:13</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:20:28</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:22:57</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:24:08</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:25:58</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:28:04</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:29:05</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:55:58</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>2026-10-24 10:58:52</t>
-  </si>
-  <si>
     <t>2026-10-24 11:01:00</t>
   </si>
   <si>
@@ -1217,6 +1250,12 @@
   </si>
   <si>
     <t>2.54</t>
+  </si>
+  <si>
+    <t>{on:SO26070626606,pc:C2988648,pm:HoLLR1206-1W-5mR-1%,qty:10,mc:,cc:1,pdi:223785763,hp:11}</t>
+  </si>
+  <si>
+    <t>2.019</t>
   </si>
   <si>
     <t>界面语言</t>
@@ -2165,6 +2204,44 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="533400" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2275,135 +2352,135 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>432</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C2" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>312</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>295</v>
-      </c>
       <c r="F2" t="s" s="0">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="J2" t="s" s="0">
         <v>34</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="L2" t="s" s="0">
         <v>34</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="N2" t="s" s="0">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="O2" t="s" s="0">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="P2" t="s" s="0">
         <v>34</v>
@@ -2412,23 +2489,23 @@
         <v>34</v>
       </c>
       <c r="R2" t="s" s="0">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="S2" s="0"/>
       <c r="T2" t="s" s="0">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="U2" t="s" s="0">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="V2" t="s" s="0">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="W2" t="s" s="0">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="X2" t="s" s="0">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="Y2" t="s" s="0">
         <v>32</v>
@@ -2459,10 +2536,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2">
@@ -2483,66 +2560,66 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>442</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>444</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>446</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>448</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>449</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -2561,10 +2638,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2863,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="15" max="15" width="16.0" customWidth="true"/>
@@ -3992,6 +4069,49 @@
       </c>
       <c r="O30" s="0"/>
     </row>
+    <row r="31" ht="72.0" customHeight="true">
+      <c r="A31" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>279</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="I31" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="K31" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="L31" s="0"/>
+      <c r="M31" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="O31" s="0"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
@@ -4013,19 +4133,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>51</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>30</v>
@@ -4033,22 +4153,22 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -4058,7 +4178,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.0" customWidth="true"/>
@@ -4070,16 +4190,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="E1" t="s" s="0">
         <v>49</v>
@@ -4087,16 +4207,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>64</v>
@@ -4104,16 +4224,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>70</v>
@@ -4121,13 +4241,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>5</v>
@@ -4138,16 +4258,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>80</v>
@@ -4155,16 +4275,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>86</v>
@@ -4172,16 +4292,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>91</v>
@@ -4189,13 +4309,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>5</v>
@@ -4206,16 +4326,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>99</v>
@@ -4223,16 +4343,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>104</v>
@@ -4240,13 +4360,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>20</v>
@@ -4257,16 +4377,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>109</v>
@@ -4274,16 +4394,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>129</v>
@@ -4291,16 +4411,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="C14" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="B14" t="s" s="0">
-        <v>280</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>295</v>
-      </c>
       <c r="D14" t="s" s="0">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>133</v>
@@ -4308,16 +4428,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>141</v>
@@ -4325,16 +4445,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>148</v>
@@ -4342,16 +4462,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>158</v>
@@ -4359,16 +4479,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>166</v>
@@ -4376,16 +4496,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>173</v>
@@ -4393,16 +4513,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>181</v>
@@ -4410,16 +4530,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>189</v>
@@ -4427,16 +4547,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>198</v>
@@ -4444,16 +4564,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C23" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="D23" t="s" s="0">
         <v>289</v>
-      </c>
-      <c r="D23" t="s" s="0">
-        <v>280</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>205</v>
@@ -4461,13 +4581,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>20</v>
@@ -4478,16 +4598,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>222</v>
@@ -4495,16 +4615,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>231</v>
@@ -4512,16 +4632,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>242</v>
@@ -4529,16 +4649,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>249</v>
@@ -4546,16 +4666,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>256</v>
@@ -4563,19 +4683,36 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>266</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>298</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>297</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -4585,7 +4722,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.0" customWidth="true"/>
@@ -4600,13 +4737,13 @@
         <v>49</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>10</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="E1" t="s" s="0">
         <v>62</v>
@@ -4620,13 +4757,13 @@
         <v>31</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3">
@@ -4637,7 +4774,7 @@
         <v>31</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>74</v>
@@ -4654,7 +4791,7 @@
         <v>31</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>79</v>
@@ -4671,13 +4808,13 @@
         <v>31</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6">
@@ -4688,7 +4825,7 @@
         <v>31</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>90</v>
@@ -4705,13 +4842,13 @@
         <v>31</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8">
@@ -4722,7 +4859,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>98</v>
@@ -4739,7 +4876,7 @@
         <v>31</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>103</v>
@@ -4756,7 +4893,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>108</v>
@@ -4773,13 +4910,13 @@
         <v>31</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>331</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12">
@@ -4790,7 +4927,7 @@
         <v>41</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>44</v>
@@ -4807,7 +4944,7 @@
         <v>31</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>132</v>
@@ -4824,13 +4961,13 @@
         <v>31</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>333</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15">
@@ -4841,13 +4978,13 @@
         <v>41</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16">
@@ -4858,13 +4995,13 @@
         <v>41</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17">
@@ -4875,13 +5012,13 @@
         <v>41</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18">
@@ -4892,13 +5029,13 @@
         <v>41</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19">
@@ -4909,13 +5046,13 @@
         <v>41</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20">
@@ -4926,7 +5063,7 @@
         <v>41</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>43</v>
@@ -4943,7 +5080,7 @@
         <v>31</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>197</v>
@@ -4960,7 +5097,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>48</v>
@@ -4977,7 +5114,7 @@
         <v>31</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>211</v>
@@ -4994,7 +5131,7 @@
         <v>31</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>221</v>
@@ -5011,7 +5148,7 @@
         <v>31</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>230</v>
@@ -5028,13 +5165,13 @@
         <v>31</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>344</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27">
@@ -5045,7 +5182,7 @@
         <v>31</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>248</v>
@@ -5062,13 +5199,13 @@
         <v>31</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29">
@@ -5079,13 +5216,13 @@
         <v>31</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>37</v>
+        <v>357</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>37</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30">
@@ -5096,13 +5233,30 @@
         <v>45</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>347</v>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -5112,7 +5266,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.0" customWidth="true"/>
@@ -5129,42 +5283,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>49</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="I1" t="s" s="0">
         <v>59</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>64</v>
@@ -5173,26 +5327,26 @@
         <v>31</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>64</v>
       </c>
       <c r="G2" s="0"/>
       <c r="H2" t="s" s="0">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="I2" s="0"/>
       <c r="J2" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>70</v>
@@ -5201,7 +5355,7 @@
         <v>31</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>70</v>
@@ -5212,15 +5366,15 @@
       </c>
       <c r="I3" s="0"/>
       <c r="J3" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>75</v>
@@ -5229,7 +5383,7 @@
         <v>31</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>75</v>
@@ -5240,15 +5394,15 @@
       </c>
       <c r="I4" s="0"/>
       <c r="J4" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>80</v>
@@ -5257,26 +5411,26 @@
         <v>31</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>80</v>
       </c>
       <c r="G5" s="0"/>
       <c r="H5" t="s" s="0">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="I5" s="0"/>
       <c r="J5" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>86</v>
@@ -5285,7 +5439,7 @@
         <v>31</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>86</v>
@@ -5296,15 +5450,15 @@
       </c>
       <c r="I6" s="0"/>
       <c r="J6" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>91</v>
@@ -5313,26 +5467,26 @@
         <v>31</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>91</v>
       </c>
       <c r="G7" s="0"/>
       <c r="H7" t="s" s="0">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="I7" s="0"/>
       <c r="J7" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s" s="0">
         <v>95</v>
@@ -5341,7 +5495,7 @@
         <v>31</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>95</v>
@@ -5352,15 +5506,15 @@
       </c>
       <c r="I8" s="0"/>
       <c r="J8" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>99</v>
@@ -5369,7 +5523,7 @@
         <v>31</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>99</v>
@@ -5380,15 +5534,15 @@
       </c>
       <c r="I9" s="0"/>
       <c r="J9" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>104</v>
@@ -5397,7 +5551,7 @@
         <v>31</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F10" t="s" s="0">
         <v>104</v>
@@ -5408,15 +5562,15 @@
       </c>
       <c r="I10" s="0"/>
       <c r="J10" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>109</v>
@@ -5425,30 +5579,30 @@
         <v>31</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>109</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>117</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>120</v>
@@ -5457,13 +5611,13 @@
         <v>41</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F12" t="s" s="0">
         <v>120</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>44</v>
@@ -5472,15 +5626,15 @@
         <v>126</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>129</v>
@@ -5489,7 +5643,7 @@
         <v>31</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F13" t="s" s="0">
         <v>129</v>
@@ -5500,15 +5654,15 @@
       </c>
       <c r="I13" s="0"/>
       <c r="J13" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>133</v>
@@ -5517,30 +5671,30 @@
         <v>31</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F14" t="s" s="0">
         <v>133</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>138</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>141</v>
@@ -5549,30 +5703,30 @@
         <v>41</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F15" t="s" s="0">
         <v>141</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>145</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>148</v>
@@ -5581,30 +5735,30 @@
         <v>41</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F16" t="s" s="0">
         <v>148</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>155</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>368</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>158</v>
@@ -5613,16 +5767,16 @@
         <v>41</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F17" t="s" s="0">
         <v>158</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>163</v>
@@ -5633,10 +5787,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>166</v>
@@ -5645,30 +5799,30 @@
         <v>41</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F18" t="s" s="0">
         <v>166</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>170</v>
       </c>
       <c r="J18" t="s" s="0">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>173</v>
@@ -5677,30 +5831,30 @@
         <v>41</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F19" t="s" s="0">
         <v>173</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>178</v>
       </c>
       <c r="J19" t="s" s="0">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>181</v>
@@ -5709,7 +5863,7 @@
         <v>41</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="F20" t="s" s="0">
         <v>181</v>
@@ -5722,15 +5876,15 @@
         <v>187</v>
       </c>
       <c r="J20" t="s" s="0">
-        <v>375</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>189</v>
@@ -5739,13 +5893,13 @@
         <v>31</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F21" t="s" s="0">
         <v>189</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>197</v>
@@ -5754,15 +5908,15 @@
         <v>195</v>
       </c>
       <c r="J21" t="s" s="0">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>198</v>
@@ -5771,13 +5925,13 @@
         <v>45</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F22" t="s" s="0">
         <v>198</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>48</v>
@@ -5786,15 +5940,15 @@
         <v>202</v>
       </c>
       <c r="J22" t="s" s="0">
-        <v>379</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>205</v>
@@ -5803,13 +5957,13 @@
         <v>31</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F23" t="s" s="0">
         <v>205</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>211</v>
@@ -5818,15 +5972,15 @@
         <v>209</v>
       </c>
       <c r="J23" t="s" s="0">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>212</v>
@@ -5835,13 +5989,13 @@
         <v>31</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F24" t="s" s="0">
         <v>212</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>221</v>
@@ -5850,15 +6004,15 @@
         <v>219</v>
       </c>
       <c r="J24" t="s" s="0">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>222</v>
@@ -5867,13 +6021,13 @@
         <v>31</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F25" t="s" s="0">
         <v>222</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>230</v>
@@ -5882,15 +6036,15 @@
         <v>228</v>
       </c>
       <c r="J25" t="s" s="0">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>231</v>
@@ -5899,30 +6053,30 @@
         <v>31</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F26" t="s" s="0">
         <v>231</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>239</v>
       </c>
       <c r="J26" t="s" s="0">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>231</v>
@@ -5931,30 +6085,30 @@
         <v>31</v>
       </c>
       <c r="E27" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F27" t="s" s="0">
         <v>231</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>239</v>
       </c>
       <c r="J27" t="s" s="0">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>242</v>
@@ -5963,13 +6117,13 @@
         <v>31</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F28" t="s" s="0">
         <v>242</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>248</v>
@@ -5978,15 +6132,15 @@
         <v>246</v>
       </c>
       <c r="J28" t="s" s="0">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="B29" t="s" s="0">
         <v>355</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>345</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>249</v>
@@ -5995,30 +6149,30 @@
         <v>31</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F29" t="s" s="0">
         <v>249</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>253</v>
       </c>
       <c r="J29" t="s" s="0">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>256</v>
@@ -6027,30 +6181,30 @@
         <v>31</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F30" t="s" s="0">
         <v>256</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>37</v>
+        <v>357</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>263</v>
       </c>
       <c r="J30" t="s" s="0">
-        <v>395</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>266</v>
@@ -6059,22 +6213,54 @@
         <v>45</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F31" t="s" s="0">
         <v>266</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>273</v>
       </c>
       <c r="J31" t="s" s="0">
-        <v>397</v>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>409</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -6099,31 +6285,31 @@
         <v>33</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0"/>
       <c r="B2" t="s" s="0">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>404</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
